--- a/Outcome/Appendix/Tables/Threshold_sensitivity_summary.xlsx
+++ b/Outcome/Appendix/Tables/Threshold_sensitivity_summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t xml:space="preserve">Threshold</t>
   </si>
@@ -60,6 +60,15 @@
   </si>
   <si>
     <t xml:space="preserve">95% / 4 mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% / 2 mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% / 3 mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% / 4 mo</t>
   </si>
 </sst>
 </file>
@@ -422,10 +431,10 @@
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>54.2</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="3">
@@ -482,10 +491,10 @@
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>8.3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="6">
@@ -502,10 +511,10 @@
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>54.2</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="7">
@@ -542,10 +551,10 @@
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>29.2</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="9">
@@ -562,10 +571,10 @@
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="10">
@@ -582,10 +591,10 @@
         <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>54.2</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="11">
@@ -622,10 +631,10 @@
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>29.2</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="13">
@@ -642,10 +651,10 @@
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="14">
@@ -662,10 +671,10 @@
         <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" t="n">
-        <v>54.2</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="15">
@@ -722,10 +731,10 @@
         <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>8.3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="18">
@@ -742,10 +751,10 @@
         <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F18" t="n">
-        <v>54.2</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="19">
@@ -782,10 +791,10 @@
         <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>29.2</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="21">
@@ -802,10 +811,10 @@
         <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="22">
@@ -822,10 +831,10 @@
         <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F22" t="n">
-        <v>54.2</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="23">
@@ -862,10 +871,10 @@
         <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>29.2</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="25">
@@ -882,10 +891,250 @@
         <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" t="n">
+        <v>14</v>
+      </c>
+      <c r="F26" t="n">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" t="n">
+        <v>14</v>
+      </c>
+      <c r="F30" t="n">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" t="n">
+        <v>14</v>
+      </c>
+      <c r="F34" t="n">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" t="n">
+        <v>8</v>
+      </c>
+      <c r="F36" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.2</v>
       </c>
     </row>
   </sheetData>
